--- a/demo_data/sectors/insaat_taahhut/ar_aging.xlsx
+++ b/demo_data/sectors/insaat_taahhut/ar_aging.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46010</v>
+        <v>46018</v>
       </c>
       <c r="D2" t="n">
-        <v>676712.33</v>
+        <v>423607.09</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46007</v>
+        <v>46020</v>
       </c>
       <c r="D3" t="n">
-        <v>676712.33</v>
+        <v>423607.09</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kalyon Altyapı Yatırımları A.Ş.</t>
+          <t>Borusan Lojistik &amp; Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46064</v>
+        <v>46000</v>
       </c>
       <c r="D4" t="n">
-        <v>1184246.58</v>
+        <v>423607.09</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Şişecam Düzcam Pazarlama A.Ş.</t>
+          <t>Kalyon Altyapı Yatırımları A.Ş.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46027</v>
+        <v>46080</v>
       </c>
       <c r="D5" t="n">
-        <v>507534.25</v>
+        <v>1111968.62</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="D6" t="n">
-        <v>507534.25</v>
+        <v>317705.32</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Eczacıbaşı Yapı Gereçleri A.Ş.</t>
+          <t>Şişecam Düzcam Pazarlama A.Ş.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46054</v>
+        <v>46008</v>
       </c>
       <c r="D7" t="n">
-        <v>1015068.49</v>
+        <v>317705.32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vestel Beyaz Eşya Sanayi A.Ş.</t>
+          <t>Şişecam Düzcam Pazarlama A.Ş.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46041</v>
+        <v>46007</v>
       </c>
       <c r="D8" t="n">
-        <v>281963.47</v>
+        <v>317705.32</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vestel Beyaz Eşya Sanayi A.Ş.</t>
+          <t>Eczacıbaşı Yapı Gereçleri A.Ş.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="D9" t="n">
-        <v>281963.47</v>
+        <v>953115.96</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>46041</v>
+        <v>46033</v>
       </c>
       <c r="D10" t="n">
-        <v>281963.47</v>
+        <v>397131.65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Arçelik Pazarlama A.Ş.</t>
+          <t>Vestel Beyaz Eşya Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -678,10 +678,10 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>46006</v>
+        <v>46034</v>
       </c>
       <c r="D11" t="n">
-        <v>422945.21</v>
+        <v>397131.65</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -701,10 +701,10 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>46004</v>
+        <v>45987</v>
       </c>
       <c r="D12" t="n">
-        <v>422945.21</v>
+        <v>794263.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>46098</v>
+        <v>46094</v>
       </c>
       <c r="D13" t="n">
-        <v>845890.41</v>
+        <v>794263.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46008</v>
+        <v>46025</v>
       </c>
       <c r="D14" t="n">
-        <v>338356.16</v>
+        <v>211803.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46018</v>
+        <v>46022</v>
       </c>
       <c r="D15" t="n">
-        <v>338356.16</v>
+        <v>211803.55</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BİM Birleşik Mağazalar A.Ş.</t>
+          <t>Tofaş Türk Otomobil Fabrikası</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46033</v>
+        <v>46015</v>
       </c>
       <c r="D16" t="n">
-        <v>225570.78</v>
+        <v>211803.54</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46023</v>
+        <v>46027</v>
       </c>
       <c r="D17" t="n">
-        <v>225570.78</v>
+        <v>635410.64</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BİM Birleşik Mağazalar A.Ş.</t>
+          <t>Migros Ticaret Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -842,7 +842,7 @@
         <v>46040</v>
       </c>
       <c r="D18" t="n">
-        <v>225570.78</v>
+        <v>635410.64</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Migros Ticaret Dağıtım A.Ş.</t>
+          <t>Anadolu Efes Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46036</v>
+        <v>46002</v>
       </c>
       <c r="D19" t="n">
-        <v>338356.16</v>
+        <v>211803.55</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Migros Ticaret Dağıtım A.Ş.</t>
+          <t>Anadolu Efes Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46047</v>
+        <v>46000</v>
       </c>
       <c r="D20" t="n">
-        <v>338356.16</v>
+        <v>211803.55</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46017</v>
+        <v>45994</v>
       </c>
       <c r="D21" t="n">
-        <v>676712.33</v>
+        <v>211803.54</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="D22" t="n">
-        <v>592123.29</v>
+        <v>185328.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Trendyol Pazaryeri Satış A.Ş.</t>
+          <t>Ülker Bisküvi Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>45970</v>
+        <v>46050</v>
       </c>
       <c r="D23" t="n">
-        <v>296061.64</v>
+        <v>185328.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Trendyol Pazaryeri Satış A.Ş.</t>
+          <t>Ülker Bisküvi Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>45974</v>
+        <v>46063</v>
       </c>
       <c r="D24" t="n">
-        <v>296061.64</v>
+        <v>185328.11</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hepsiburada E-Ticaret A.Ş.</t>
+          <t>Trendyol Pazaryeri Satış A.Ş.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46017</v>
+        <v>45968</v>
       </c>
       <c r="D25" t="n">
-        <v>253767.12</v>
+        <v>185328.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hepsiburada E-Ticaret A.Ş.</t>
+          <t>Trendyol Pazaryeri Satış A.Ş.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46016</v>
+        <v>45972</v>
       </c>
       <c r="D26" t="n">
-        <v>253767.12</v>
+        <v>185328.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LC Waikiki Mağazacılık A.Ş.</t>
+          <t>Trendyol Pazaryeri Satış A.Ş.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46103</v>
+        <v>45974</v>
       </c>
       <c r="D27" t="n">
-        <v>507534.25</v>
+        <v>185328.11</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DeFacto Perakende Ticaret A.Ş.</t>
+          <t>Hepsiburada E-Ticaret A.Ş.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46035</v>
+        <v>45998</v>
       </c>
       <c r="D28" t="n">
-        <v>507534.25</v>
+        <v>158852.66</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Turkcell İletişim Hizmetleri A.Ş.</t>
+          <t>Hepsiburada E-Ticaret A.Ş.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46106</v>
+        <v>46009</v>
       </c>
       <c r="D29" t="n">
-        <v>211472.6</v>
+        <v>158852.66</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Turkcell İletişim Hizmetleri A.Ş.</t>
+          <t>Hepsiburada E-Ticaret A.Ş.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46114</v>
+        <v>45999</v>
       </c>
       <c r="D30" t="n">
-        <v>211472.6</v>
+        <v>158852.66</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vodafone Telekomünikasyon A.Ş.</t>
+          <t>LC Waikiki Mağazacılık A.Ş.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46020</v>
+        <v>46096</v>
       </c>
       <c r="D31" t="n">
-        <v>140981.74</v>
+        <v>238278.99</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Vodafone Telekomünikasyon A.Ş.</t>
+          <t>LC Waikiki Mağazacılık A.Ş.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46018</v>
+        <v>46111</v>
       </c>
       <c r="D32" t="n">
-        <v>140981.74</v>
+        <v>238278.99</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Vodafone Telekomünikasyon A.Ş.</t>
+          <t>DeFacto Perakende Ticaret A.Ş.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46024</v>
+        <v>46034</v>
       </c>
       <c r="D33" t="n">
-        <v>140981.74</v>
+        <v>238278.99</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Türk Telekomünikasyon A.Ş.</t>
+          <t>DeFacto Perakende Ticaret A.Ş.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46047</v>
+        <v>46026</v>
       </c>
       <c r="D34" t="n">
-        <v>140981.74</v>
+        <v>238278.99</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Türk Telekomünikasyon A.Ş.</t>
+          <t>Turkcell İletişim Hizmetleri A.Ş.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46066</v>
+        <v>46116</v>
       </c>
       <c r="D35" t="n">
-        <v>140981.74</v>
+        <v>132377.22</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Türk Telekomünikasyon A.Ş.</t>
+          <t>Turkcell İletişim Hizmetleri A.Ş.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46057</v>
+        <v>46102</v>
       </c>
       <c r="D36" t="n">
-        <v>140981.74</v>
+        <v>132377.22</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aselsan Elektronik Sanayi A.Ş.</t>
+          <t>Turkcell İletişim Hizmetleri A.Ş.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46122</v>
+        <v>46113</v>
       </c>
       <c r="D37" t="n">
-        <v>422945.21</v>
+        <v>132377.21</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Havelsan Hava Elektronik Sanayi</t>
+          <t>Vodafone Telekomünikasyon A.Ş.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46004</v>
+        <v>46016</v>
       </c>
       <c r="D38" t="n">
-        <v>112785.39</v>
+        <v>397131.65</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Havelsan Hava Elektronik Sanayi</t>
+          <t>Türk Telekomünikasyon A.Ş.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46002</v>
+        <v>46067</v>
       </c>
       <c r="D39" t="n">
-        <v>112785.39</v>
+        <v>132377.22</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Havelsan Hava Elektronik Sanayi</t>
+          <t>Türk Telekomünikasyon A.Ş.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46010</v>
+        <v>46051</v>
       </c>
       <c r="D40" t="n">
-        <v>112785.39</v>
+        <v>132377.22</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tekfen İnşaat ve Tesisat A.Ş.</t>
+          <t>Türk Telekomünikasyon A.Ş.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46138</v>
+        <v>46065</v>
       </c>
       <c r="D41" t="n">
-        <v>338356.16</v>
+        <v>132377.21</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Limak İnşaat Sanayi ve Ticaret</t>
+          <t>Aselsan Elektronik Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46077</v>
+        <v>46129</v>
       </c>
       <c r="D42" t="n">
-        <v>338356.16</v>
+        <v>132377.22</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cengiz İnşaat Sanayi A.Ş.</t>
+          <t>Aselsan Elektronik Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46113</v>
+        <v>46136</v>
       </c>
       <c r="D43" t="n">
-        <v>169178.08</v>
+        <v>132377.22</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cengiz İnşaat Sanayi A.Ş.</t>
+          <t>Aselsan Elektronik Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46106</v>
+        <v>46133</v>
       </c>
       <c r="D44" t="n">
-        <v>169178.08</v>
+        <v>132377.21</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>İÇDAŞ Çelik Enerji Tersane A.Ş.</t>
+          <t>Havelsan Hava Elektronik Sanayi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46029</v>
+        <v>46017</v>
       </c>
       <c r="D45" t="n">
-        <v>112785.39</v>
+        <v>105901.77</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>İÇDAŞ Çelik Enerji Tersane A.Ş.</t>
+          <t>Havelsan Hava Elektronik Sanayi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="D46" t="n">
-        <v>112785.39</v>
+        <v>105901.77</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>İÇDAŞ Çelik Enerji Tersane A.Ş.</t>
+          <t>Havelsan Hava Elektronik Sanayi</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46031</v>
+        <v>46026</v>
       </c>
       <c r="D47" t="n">
-        <v>112785.39</v>
+        <v>105901.78</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kardemir Karabük Demir Çelik</t>
+          <t>Tekfen İnşaat ve Tesisat A.Ş.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46045</v>
+        <v>46160</v>
       </c>
       <c r="D48" t="n">
-        <v>126883.56</v>
+        <v>317705.32</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kardemir Karabük Demir Çelik</t>
+          <t>Limak İnşaat Sanayi ve Ticaret</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46054</v>
+        <v>46076</v>
       </c>
       <c r="D49" t="n">
-        <v>126883.56</v>
+        <v>105901.77</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Akçansa Çimento Sanayi A.Ş.</t>
+          <t>Limak İnşaat Sanayi ve Ticaret</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>46074</v>
+        <v>46077</v>
       </c>
       <c r="D50" t="n">
-        <v>126883.56</v>
+        <v>105901.77</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Akçansa Çimento Sanayi A.Ş.</t>
+          <t>Limak İnşaat Sanayi ve Ticaret</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>46092</v>
+        <v>46059</v>
       </c>
       <c r="D51" t="n">
-        <v>126883.56</v>
+        <v>105901.78</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Çimsa Çimento Sanayi A.Ş.</t>
+          <t>Cengiz İnşaat Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46044</v>
+        <v>46097</v>
       </c>
       <c r="D52" t="n">
-        <v>84589.03999999999</v>
+        <v>317705.32</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Çimsa Çimento Sanayi A.Ş.</t>
+          <t>İÇDAŞ Çelik Enerji Tersane A.Ş.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>46046</v>
+        <v>46007</v>
       </c>
       <c r="D53" t="n">
-        <v>84589.03999999999</v>
+        <v>158852.66</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Çimsa Çimento Sanayi A.Ş.</t>
+          <t>İÇDAŞ Çelik Enerji Tersane A.Ş.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>46031</v>
+        <v>46014</v>
       </c>
       <c r="D54" t="n">
-        <v>84589.03999999999</v>
+        <v>158852.66</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Petkim Petrokimya Holding A.Ş.</t>
+          <t>Kardemir Karabük Demir Çelik</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>45989</v>
+        <v>46043</v>
       </c>
       <c r="D55" t="n">
-        <v>126883.56</v>
+        <v>79426.33</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Petkim Petrokimya Holding A.Ş.</t>
+          <t>Kardemir Karabük Demir Çelik</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>45996</v>
+        <v>46052</v>
       </c>
       <c r="D56" t="n">
-        <v>126883.56</v>
+        <v>79426.33</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tüpraş Türkiye Petrol Rafinerileri</t>
+          <t>Kardemir Karabük Demir Çelik</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>46033</v>
+        <v>46054</v>
       </c>
       <c r="D57" t="n">
-        <v>253767.12</v>
+        <v>79426.33</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Doğuş Otomotiv Servis ve Ticaret</t>
+          <t>Akçansa Çimento Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>46067</v>
+        <v>46082</v>
       </c>
       <c r="D58" t="n">
-        <v>169178.08</v>
+        <v>238278.99</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Koçtaş Yapı Marketleri A.Ş.</t>
+          <t>Çimsa Çimento Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>46074</v>
+        <v>46051</v>
       </c>
       <c r="D59" t="n">
-        <v>169178.08</v>
+        <v>238278.99</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Teknosa İç ve Dış Ticaret A.Ş.</t>
+          <t>Petkim Petrokimya Holding A.Ş.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>46094</v>
+        <v>45999</v>
       </c>
       <c r="D60" t="n">
-        <v>84589.03999999999</v>
+        <v>79426.33</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Teknosa İç ve Dış Ticaret A.Ş.</t>
+          <t>Petkim Petrokimya Holding A.Ş.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>46100</v>
+        <v>46010</v>
       </c>
       <c r="D61" t="n">
-        <v>84589.03999999999</v>
+        <v>79426.33</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CarrefourSA Hipermarketleri A.Ş.</t>
+          <t>Petkim Petrokimya Holding A.Ş.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>46024</v>
+        <v>46010</v>
       </c>
       <c r="D62" t="n">
-        <v>56392.69</v>
+        <v>79426.33</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CarrefourSA Hipermarketleri A.Ş.</t>
+          <t>Tüpraş Türkiye Petrol Rafinerileri</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1877,7 +1877,7 @@
         <v>46020</v>
       </c>
       <c r="D63" t="n">
-        <v>56392.69</v>
+        <v>119139.49</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CarrefourSA Hipermarketleri A.Ş.</t>
+          <t>Tüpraş Türkiye Petrol Rafinerileri</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>46021</v>
+        <v>46023</v>
       </c>
       <c r="D64" t="n">
-        <v>56392.69</v>
+        <v>119139.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Şok Marketler Ticaret A.Ş.</t>
+          <t>Doğuş Otomotiv Servis ve Ticaret</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>46022</v>
+        <v>46049</v>
       </c>
       <c r="D65" t="n">
-        <v>56392.69</v>
+        <v>52950.89</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Şok Marketler Ticaret A.Ş.</t>
+          <t>Doğuş Otomotiv Servis ve Ticaret</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>46029</v>
+        <v>46055</v>
       </c>
       <c r="D66" t="n">
-        <v>56392.69</v>
+        <v>52950.89</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1957,21 +1957,182 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>Doğuş Otomotiv Servis ve Ticaret</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FA-1066</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="D67" t="n">
+        <v>52950.88</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Koçtaş Yapı Marketleri A.Ş.</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FA-1067</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>46061</v>
+      </c>
+      <c r="D68" t="n">
+        <v>158852.66</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Teknosa İç ve Dış Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FA-1068</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="D69" t="n">
+        <v>52950.89</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Teknosa İç ve Dış Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>FA-1069</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D70" t="n">
+        <v>52950.89</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Teknosa İç ve Dış Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FA-1070</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D71" t="n">
+        <v>52950.88</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CarrefourSA Hipermarketleri A.Ş.</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FA-1071</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="D72" t="n">
+        <v>158852.66</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>Şok Marketler Ticaret A.Ş.</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>FA-1066</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="n">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FA-1072</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
         <v>46042</v>
       </c>
-      <c r="D67" t="n">
-        <v>56392.69</v>
-      </c>
-      <c r="E67" t="inlineStr">
+      <c r="D73" t="n">
+        <v>79426.3</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Şok Marketler Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FA-1073</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="D74" t="n">
+        <v>79426.3</v>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>TL</t>
         </is>
